--- a/Hackathons/Cogizant Technoverse Hackathon 2026/Only_3_Teams_From_Campus_Selected_[12 Students].xlsx
+++ b/Hackathons/Cogizant Technoverse Hackathon 2026/Only_3_Teams_From_Campus_Selected_[12 Students].xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\College Cut 2026\Tech_ABC\West &amp; Central\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\GitHub-Repositories\Wisdom-Primary-Repo\Hackathons\Cogizant Technoverse Hackathon 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F46402-E37B-4367-B0DE-32A13E2D4543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9FFA55-D944-4958-8B4C-404B7224482B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5F99E9FD-1A51-4C1F-9E1D-3E1ADE2E52BD}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{5F99E9FD-1A51-4C1F-9E1D-3E1ADE2E52BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Consolidated" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -165,7 +165,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,12 +571,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8513EF70-28D6-40AB-B07E-BE2EAF239B4F}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="9" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="50.75" customWidth="1"/>
+    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="25.375" customWidth="1"/>
+    <col min="4" max="4" width="41.75" customWidth="1"/>
+    <col min="5" max="5" width="22.75" customWidth="1"/>
+    <col min="6" max="6" width="22.5" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="9" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -634,7 +641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -663,7 +670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -692,7 +699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -721,7 +728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -750,7 +757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -779,7 +786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -808,7 +815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -837,7 +844,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -866,7 +873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -895,7 +902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
@@ -924,7 +931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
@@ -959,6 +966,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C0E60DD53B08764D9FBA21DBED3214CC" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd4086fc227d84930da0763be3e0042">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0a84972d-ef8c-45a9-9686-55cfd8231be0" xmlns:ns3="1eec79b3-321e-4dfa-8d23-6bc73fc62350" xmlns:ns4="3c35e321-f73a-4dae-ae38-a0459de24735" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8be992cee903fad960eda9f235136ae" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="0a84972d-ef8c-45a9-9686-55cfd8231be0"/>
@@ -1244,15 +1260,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1268,13 +1275,40 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74259387-7EEB-4AEC-9FEC-E9CC256EC9DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{934965A7-ECFC-45AD-84BA-D9E5814D0793}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{934965A7-ECFC-45AD-84BA-D9E5814D0793}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74259387-7EEB-4AEC-9FEC-E9CC256EC9DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0a84972d-ef8c-45a9-9686-55cfd8231be0"/>
+    <ds:schemaRef ds:uri="1eec79b3-321e-4dfa-8d23-6bc73fc62350"/>
+    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE4C942-4B73-4843-AE14-2E31459FFE6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE4C942-4B73-4843-AE14-2E31459FFE6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0a84972d-ef8c-45a9-9686-55cfd8231be0"/>
+    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>